--- a/data/trans_orig/P42-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2007</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2007 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>966</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>978538</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>947618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1011969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>947588</t>
+          <t>947618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1012962</t>
+          <t>1011969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,42 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>978538</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>947588</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1012962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>74,98%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>72,61%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>77,62%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326514</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292090</t>
+          <t>293083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357464</t>
+          <t>357434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,45 +801,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>326514</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>292090</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>357464</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>27,39%</t>
         </is>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305052</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1305052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1305052</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1305052</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1305052</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1265618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1232370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1297471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1231440</t>
+          <t>1232370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1294354</t>
+          <t>1297471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1265618</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1231440</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1294354</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>77,75%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318184</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289448</t>
+          <t>286331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352362</t>
+          <t>351432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>318184</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>289448</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>352362</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583802</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583802</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1583802</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1583802</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1583802</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417199</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>402668</t>
+          <t>402904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>430391</t>
+          <t>430196</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>417199</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>402668</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>430391</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>84,73%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58045</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44853</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72576</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>58045</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>44853</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>72576</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>451</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>475244</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>475244</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>475244</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2609848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2707448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2615119</t>
+          <t>2609848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2706419</t>
+          <t>2707448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2615119</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2706419</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>77,74%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>702743</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657680</t>
+          <t>656651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>748980</t>
+          <t>754251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>702743</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>657680</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>748980</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3284</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2090,13 +1610,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2110,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2129,25 +1648,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2012</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2012 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +1670,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2167,17 +1679,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2248,41 +1749,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2305,13 +1771,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2326,37 +1785,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1136152</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1111565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1163214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1109638</t>
+          <t>1111565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1163401</t>
+          <t>1163214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,47 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1136152</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1109638</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1163401</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -2439,37 +1863,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197603</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170354</t>
+          <t>170541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224117</t>
+          <t>222190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,47 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>197603</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>170354</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>224117</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -2552,37 +1941,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1333755</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1333755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1333755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2616,41 +2005,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1333755</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1333755</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1333755</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1522734</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1491385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1547524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1492059</t>
+          <t>1491385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1548819</t>
+          <t>1547524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,47 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1522734</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1492059</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1548819</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219071</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192986</t>
+          <t>194281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249746</t>
+          <t>250420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,47 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>219071</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>192986</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>249746</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1741805</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1741805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1741805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1620</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1741805</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1741805</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1741805</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421344</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>407452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>408356</t>
+          <t>407452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432556</t>
+          <t>431948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,47 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>421344</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>408356</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>432556</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36211</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49199</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,47 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>36211</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>24999</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>49199</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>411</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>457555</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>457555</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>457555</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3080230</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3040809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3118884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3039686</t>
+          <t>3040809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3122716</t>
+          <t>3118884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,47 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3080230</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3039686</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3122716</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>86,03%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452884</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410398</t>
+          <t>414230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493428</t>
+          <t>492305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,47 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>452884</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>410398</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>493428</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3533114</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3533114</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3533114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3533114</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3533114</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3533114</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3693,13 +2732,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3713,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3732,25 +2770,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2016</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +2792,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3770,17 +2801,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3851,41 +2871,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3908,13 +2893,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3929,37 +2907,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>746</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>826185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>799587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>849638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>800365</t>
+          <t>799587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>848559</t>
+          <t>849638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,47 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>826185</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>800365</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>848559</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>86,25%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -4042,37 +2985,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157630</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135256</t>
+          <t>134177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183450</t>
+          <t>184228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,47 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>157630</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>135256</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>183450</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3063,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>983815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>983815</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>983815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4219,41 +3127,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>983815</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>983815</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>983815</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4272,37 +3145,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1724120</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1692272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1753381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1692146</t>
+          <t>1692272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1753309</t>
+          <t>1753381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,45 +3205,10 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1724120</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1692146</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1753309</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>88,76%</t>
         </is>
@@ -4385,37 +3223,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222065</t>
+          <t>221993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>283102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,42 +3288,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>251254</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>222065</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>283228</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -4498,37 +3301,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1975374</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1975374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1975374</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4562,41 +3365,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1975374</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1975374</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1975374</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4615,37 +3383,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505882</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>492781</t>
+          <t>492355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>517410</t>
+          <t>516838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>505882</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>492781</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>517410</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -4728,37 +3461,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,47 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>40661</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>29133</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>53762</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4841,37 +3539,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546543</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4905,41 +3603,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>546543</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>546543</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>546543</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4958,37 +3621,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3056188</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3015170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3094909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3013638</t>
+          <t>3015170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3093018</t>
+          <t>3094909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,47 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2872</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3056188</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3013638</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3093018</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5071,37 +3699,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449545</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>412715</t>
+          <t>410824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492095</t>
+          <t>490563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,47 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>449545</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>412715</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>492095</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -5184,37 +3777,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3505733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3505733</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3505733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5248,41 +3841,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3505733</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3505733</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3505733</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5296,13 +3854,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -5316,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5335,25 +3892,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2023</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +3914,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5373,17 +3923,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5454,41 +3993,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5511,13 +4015,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5532,37 +4029,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>519554</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>503659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>532290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +4074,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>504420</t>
+          <t>503659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>532523</t>
+          <t>532290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,47 +4089,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>519554</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>504420</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>532523</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>87,05%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -5645,37 +4107,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92163</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +4152,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>79427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107297</t>
+          <t>108058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,47 +4167,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>92163</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>79194</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>107297</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4185,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5822,41 +4249,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>611717</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>611717</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>611717</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5875,37 +4267,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1285438</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>837002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1476166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +4312,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>862224</t>
+          <t>837002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1477026</t>
+          <t>1476166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,47 +4327,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1285438</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>862224</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1477026</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -5988,37 +4345,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>272</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>462511</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>910947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +4390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270923</t>
+          <t>271783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>885725</t>
+          <t>910947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,47 +4405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>462511</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>270923</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>885725</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4423,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1747949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1747949</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1747949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6165,41 +4487,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1747949</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1747949</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1747949</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6218,37 +4505,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408963</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395784</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +4550,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>394873</t>
+          <t>395784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>421283</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,47 +4565,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>408963</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>394873</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>421283</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>85,75%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -6331,37 +4583,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64689</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +4628,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65600</t>
+          <t>64689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,47 +4643,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>51510</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>39190</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>65600</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -6444,37 +4661,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460473</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6508,41 +4725,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>460473</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>460473</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>460473</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6561,37 +4743,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2213955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1694699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2405115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +4788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1689695</t>
+          <t>1694699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2403283</t>
+          <t>2405115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +4803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2213955</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1689695</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2403283</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -6674,37 +4821,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>606184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1125440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +4866,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>416856</t>
+          <t>415024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1130444</t>
+          <t>1125440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,47 +4881,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>606184</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>416856</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1130444</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>21,49%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -6787,37 +4899,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2820139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2820139</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2820139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6851,41 +4963,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2820139</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2820139</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2820139</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6899,13 +4976,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P42-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>947618</t>
+          <t>947334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1011969</t>
+          <t>1008863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>947618</t>
+          <t>947334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1011969</t>
+          <t>1008863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293083</t>
+          <t>296189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357434</t>
+          <t>357718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293083</t>
+          <t>296189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357434</t>
+          <t>357718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1232370</t>
+          <t>1235521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1297471</t>
+          <t>1294419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1232370</t>
+          <t>1235521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1297471</t>
+          <t>1294419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286331</t>
+          <t>289383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>351432</t>
+          <t>348281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286331</t>
+          <t>289383</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351432</t>
+          <t>348281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>402904</t>
+          <t>403355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>430196</t>
+          <t>429480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>402904</t>
+          <t>403355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>430196</t>
+          <t>429480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>45764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72340</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>45764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72340</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1111565</t>
+          <t>1108607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1163214</t>
+          <t>1164010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1111565</t>
+          <t>1108607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1163214</t>
+          <t>1164010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170541</t>
+          <t>169745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222190</t>
+          <t>225148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170541</t>
+          <t>169745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222190</t>
+          <t>225148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1491385</t>
+          <t>1494645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1547524</t>
+          <t>1549831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1491385</t>
+          <t>1494645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1547524</t>
+          <t>1549831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194281</t>
+          <t>191974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250420</t>
+          <t>247160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194281</t>
+          <t>191974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250420</t>
+          <t>247160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>407452</t>
+          <t>406431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>431948</t>
+          <t>431366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>407452</t>
+          <t>406431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>431948</t>
+          <t>431366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>51124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>51124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3040809</t>
+          <t>3037974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3118884</t>
+          <t>3116951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3040809</t>
+          <t>3037974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3118884</t>
+          <t>3116951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414230</t>
+          <t>416163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492305</t>
+          <t>495140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>414230</t>
+          <t>416163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492305</t>
+          <t>495140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>799587</t>
+          <t>799083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>849638</t>
+          <t>848180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>799587</t>
+          <t>799083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>849638</t>
+          <t>848180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134177</t>
+          <t>135635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184228</t>
+          <t>184732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134177</t>
+          <t>135635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184228</t>
+          <t>184732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1692272</t>
+          <t>1696209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1753381</t>
+          <t>1754572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1692272</t>
+          <t>1696209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1753381</t>
+          <t>1754572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221993</t>
+          <t>220802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283102</t>
+          <t>279165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221993</t>
+          <t>220802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>283102</t>
+          <t>279165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>492355</t>
+          <t>491910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>516838</t>
+          <t>516673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>492355</t>
+          <t>491910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>516838</t>
+          <t>516673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3015170</t>
+          <t>3017409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3094909</t>
+          <t>3096773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3015170</t>
+          <t>3017409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3094909</t>
+          <t>3096773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>410824</t>
+          <t>408960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490563</t>
+          <t>488324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410824</t>
+          <t>408960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490563</t>
+          <t>488324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -4034,32 +4034,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>519554</t>
+          <t>563565</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>503659</t>
+          <t>547953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>578603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4069,32 +4069,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>519554</t>
+          <t>563565</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>503659</t>
+          <t>547953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>578603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -4112,32 +4112,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92163</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79427</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108058</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92163</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79427</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108058</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4190,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>666444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,32 +4272,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1285438</t>
+          <t>1318909</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>837002</t>
+          <t>1283290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1476166</t>
+          <t>1352850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4307,32 +4307,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1285438</t>
+          <t>1318909</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>837002</t>
+          <t>1283290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1476166</t>
+          <t>1352850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>462511</t>
+          <t>299386</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271783</t>
+          <t>265445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>910947</t>
+          <t>335005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>462511</t>
+          <t>299386</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271783</t>
+          <t>265445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910947</t>
+          <t>335005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1747949</t>
+          <t>1618295</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>408963</t>
+          <t>456686</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>395784</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>421380</t>
+          <t>468515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4545,32 +4545,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>408963</t>
+          <t>456686</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>395784</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>421380</t>
+          <t>468515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51510</t>
+          <t>53734</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>69538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51510</t>
+          <t>53734</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>69538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>510420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4748,32 +4748,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2213955</t>
+          <t>2339159</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1694699</t>
+          <t>2291424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2405115</t>
+          <t>2374868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4783,32 +4783,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2213955</t>
+          <t>2339159</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1694699</t>
+          <t>2291424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2405115</t>
+          <t>2374868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415024</t>
+          <t>420291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1125440</t>
+          <t>503735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,32 +4861,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415024</t>
+          <t>420291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1125440</t>
+          <t>503735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2820139</t>
+          <t>2795159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
